--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIV/LTAIPT_A63F34E.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIV/LTAIPT_A63F34E.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="57">
   <si>
     <t>48992</t>
   </si>
@@ -121,73 +121,70 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>0187CE7EFEA9A5E0CCE77009B5BF191A</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/04/2022</t>
-  </si>
-  <si>
-    <t>30/06/2022</t>
+    <t>785E962B0E7C60715EDB7D20646BE942</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/04/2023</t>
+  </si>
+  <si>
+    <t>30/06/2023</t>
+  </si>
+  <si>
+    <t>Predio ejidal Av. Reforma Agraria s/n Nicolás Bravo, Terrenate</t>
+  </si>
+  <si>
+    <t>Convenio</t>
+  </si>
+  <si>
+    <t>01/01/2018</t>
+  </si>
+  <si>
+    <t>Subdirección de Planeación y Evaluación</t>
+  </si>
+  <si>
+    <t>06/07/2023</t>
+  </si>
+  <si>
+    <t>NOTA</t>
+  </si>
+  <si>
+    <t>CDAF928FD6D25B9F361F490FE9D0D634</t>
+  </si>
+  <si>
+    <t>Predio ejidal Av. Pino Suárez s/n San José Xicohténcatl , Huamantla</t>
+  </si>
+  <si>
+    <t>C5EE5D6C82E2C5AE97060EC8D4BA7AAE</t>
+  </si>
+  <si>
+    <t>Predio ejidal con construcción Calle Domingo Arenas s/n San Miguel Pipillola, Españita.</t>
+  </si>
+  <si>
+    <t>92AF140860CFE75A4F6A17726C2F16EF</t>
   </si>
   <si>
     <t>Predio ejidal Av. Reforma  s/n San Francisco Cuexcontzi, Cuapiaxtla</t>
   </si>
   <si>
-    <t>Convenio</t>
-  </si>
-  <si>
-    <t>01/01/2018</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Subdirección de Planeación y Evaluación</t>
-  </si>
-  <si>
-    <t>15/07/2022</t>
-  </si>
-  <si>
-    <t>En el periodo del 1 de abril de 2022 al 30 de junio de 2022, el Colegio de Bachilleres del Estado de Tlaxcala, firmó el convenio modificatorio Institucional: Colegio de Bachilleres del Estado de Tlaxcala-Secretaría de Educación Pública del Estado-Unidad de Servicios Educativos de Tlaxcala, para coordinar el trabajo de los Telebachilleratos Comunitarios.</t>
-  </si>
-  <si>
-    <t>B7AB5A98EB5A93A850A8228FD2C77CC8</t>
-  </si>
-  <si>
-    <t>Predio ejidal con construcción Calle Domingo Arenas s/n San Miguel Pipillola, Españita.</t>
-  </si>
-  <si>
-    <t>4F7BA4EB394F51F8C6E1CD07B10A2E8F</t>
-  </si>
-  <si>
-    <t>Predio ejidal Av. Pino Suárez s/n San José Xicohténcatl , Huamantla</t>
-  </si>
-  <si>
-    <t>71F5FE20FA8727CE113B61B2DB4BAB35</t>
-  </si>
-  <si>
-    <t>Predio ejidal Av. Reforma Agraria s/n Nicolás Bravo, Terrenate</t>
-  </si>
-  <si>
-    <t>F6E6E5FC6EC89404586CA9AABCD4765F</t>
+    <t>4321F415C0E9FD99B84A5499317F016D</t>
   </si>
   <si>
     <t>Predio Ejidal con construcción Calle 16 de septiembre s/n Lagunilla, Tlaxco</t>
   </si>
   <si>
-    <t>00D83B1713F3D104052DA08629A9C9DE</t>
-  </si>
-  <si>
-    <t>AAF54676A44DC3CD360020DBE8F14C19</t>
-  </si>
-  <si>
-    <t>78095E615B2D2BD1257C7BB565B14953</t>
-  </si>
-  <si>
-    <t>E702691C8077E1417D2682DFD23BC9D9</t>
+    <t>A7F2DAA923CE6C30840C70CFB1012ECA</t>
+  </si>
+  <si>
+    <t>E9FC8DE1F1316A9C4FB19F53B26B9F66</t>
+  </si>
+  <si>
+    <t>28791BBEEF53D6EBE0DEBB489CFDB658</t>
+  </si>
+  <si>
+    <t>22A8D3E1DF4E1F4B825BDDBE2D0EC028</t>
   </si>
 </sst>
 </file>
@@ -264,7 +261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -278,9 +275,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -586,7 +580,7 @@
   <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.140625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -597,7 +591,7 @@
     <col min="9" max="9" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="20" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="255" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
@@ -781,24 +775,24 @@
         <v>41</v>
       </c>
       <c r="H8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="J8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>36</v>
@@ -810,7 +804,7 @@
         <v>38</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>40</v>
@@ -819,24 +813,24 @@
         <v>41</v>
       </c>
       <c r="H9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="J9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>36</v>
@@ -848,7 +842,7 @@
         <v>38</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>40</v>
@@ -857,24 +851,24 @@
         <v>41</v>
       </c>
       <c r="H10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="J10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L10" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>36</v>
@@ -886,7 +880,7 @@
         <v>38</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>40</v>
@@ -895,24 +889,24 @@
         <v>41</v>
       </c>
       <c r="H11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I11" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="J11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L11" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>36</v>
@@ -924,7 +918,7 @@
         <v>38</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>40</v>
@@ -933,24 +927,24 @@
         <v>41</v>
       </c>
       <c r="H12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I12" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="J12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L12" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>36</v>
@@ -971,24 +965,24 @@
         <v>41</v>
       </c>
       <c r="H13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I13" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="J13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L13" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>36</v>
@@ -1000,7 +994,7 @@
         <v>38</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>40</v>
@@ -1009,24 +1003,24 @@
         <v>41</v>
       </c>
       <c r="H14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I14" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="J14" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L14" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>36</v>
@@ -1038,7 +1032,7 @@
         <v>38</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>40</v>
@@ -1047,24 +1041,24 @@
         <v>41</v>
       </c>
       <c r="H15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="J15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L15" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>36</v>
@@ -1076,7 +1070,7 @@
         <v>38</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>40</v>
@@ -1085,19 +1079,19 @@
         <v>41</v>
       </c>
       <c r="H16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I16" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="J16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L16" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>
